--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>459.5</v>
+        <v>459.6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-19T20:25:16</t>
+          <t>2026-09-20T17:09:27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-19T20:25:16</t>
+          <t>2026-09-20T17:09:27</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>459.6</v>
+        <v>459.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-20T17:09:27</t>
+          <t>2026-09-21T20:27:41</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7669</v>
+        <v>7709</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-20T17:09:27</t>
+          <t>2026-09-21T20:27:41</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>459.5</v>
+        <v>459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-21T20:27:41</t>
+          <t>2026-09-23T19:01:55</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7709</v>
+        <v>7752.33</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-21T20:27:41</t>
+          <t>2026-09-23T19:01:55</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-23T19:01:55</t>
+          <t>2026-09-24T19:37:08</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7752.33</v>
+        <v>7719</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-23T19:01:55</t>
+          <t>2026-09-24T19:37:08</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>458</v>
+        <v>457.25</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-24T19:37:08</t>
+          <t>2026-09-27T23:12:10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-24T19:37:08</t>
+          <t>2026-09-27T23:12:10</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>457.25</v>
+        <v>457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-27T23:12:10</t>
+          <t>2026-09-28T22:41:32</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7719</v>
+        <v>7735.67</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-27T23:12:10</t>
+          <t>2026-09-28T22:41:32</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-28T22:41:32</t>
+          <t>2026-09-29T20:36:10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7735.67</v>
+        <v>7752.33</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-28T22:41:32</t>
+          <t>2026-09-29T20:36:10</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-29T20:36:10</t>
+          <t>2026-09-30T20:04:57</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7752.33</v>
+        <v>7685.67</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-29T20:36:10</t>
+          <t>2026-09-30T20:04:57</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>456</v>
+        <v>435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-30T20:04:57</t>
+          <t>2026-10-01T19:11:07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7685.67</v>
+        <v>7702.33</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-30T20:04:57</t>
+          <t>2026-10-01T19:11:07</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>435</v>
+        <v>432.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-01T19:11:07</t>
+          <t>2026-10-02T20:18:22</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-01T19:11:07</t>
+          <t>2026-10-02T20:18:22</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>432.5</v>
+        <v>446.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-02T20:18:22</t>
+          <t>2026-10-03T20:12:35</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-02T20:18:22</t>
+          <t>2026-10-03T20:12:35</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-03T20:12:35</t>
+          <t>2026-10-04T16:11:55</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-03T20:12:35</t>
+          <t>2026-10-04T16:11:55</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-04T16:11:55</t>
+          <t>2026-10-05T19:40:27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-04T16:11:55</t>
+          <t>2026-10-05T19:40:27</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>446.5</v>
+        <v>440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-05T19:40:27</t>
+          <t>2026-10-06T18:23:16</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-05T19:40:27</t>
+          <t>2026-10-06T18:23:16</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-06T18:23:16</t>
+          <t>2026-10-08T22:48:14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-06T18:23:16</t>
+          <t>2026-10-08T22:48:14</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-08T22:48:14</t>
+          <t>2026-10-08T22:49:37</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7702.33</v>
+        <v>7402.33</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-08T22:48:14</t>
+          <t>2026-10-08T22:49:37</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-08T22:49:37</t>
+          <t>2026-10-09T17:14:15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7402.33</v>
+        <v>7392.33</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-08T22:49:37</t>
+          <t>2026-10-09T17:14:15</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>441</v>
+        <v>438.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-09T17:14:15</t>
+          <t>2026-10-12T20:35:09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7392.33</v>
+        <v>7319</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-09T17:14:15</t>
+          <t>2026-10-12T20:35:09</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>438.5</v>
+        <v>450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-12T20:35:09</t>
+          <t>2026-10-14T17:14:41</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7319</v>
+        <v>7190</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-12T20:35:09</t>
+          <t>2026-10-14T17:14:41</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-14T17:14:41</t>
+          <t>2026-10-14T17:15:19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7190</v>
+        <v>7166.67</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-14T17:14:41</t>
+          <t>2026-10-14T17:15:19</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>450</v>
+        <v>461.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-14T17:15:19</t>
+          <t>2026-10-16T21:08:46</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7166.67</v>
+        <v>6669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-14T17:15:19</t>
+          <t>2026-10-16T21:08:46</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>461.5</v>
+        <v>457.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-16T21:08:46</t>
+          <t>2026-10-16T21:09:20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6669</v>
+        <v>6652.33</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-16T21:08:46</t>
+          <t>2026-10-16T21:09:20</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>457.5</v>
+        <v>455.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-16T21:09:20</t>
+          <t>2026-10-19T19:18:11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6652.33</v>
+        <v>6076.75</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-16T21:09:20</t>
+          <t>2026-10-19T19:18:11</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>455.5</v>
+        <v>444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-19T19:18:11</t>
+          <t>2026-10-29T21:27:14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6076.75</v>
+        <v>6076.8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-19T19:18:11</t>
+          <t>2026-10-29T21:27:14</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-29T21:27:14</t>
+          <t>2026-10-29T21:28:26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6076.8</v>
+        <v>5776.8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-29T21:27:14</t>
+          <t>2026-10-29T21:28:26</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>444</v>
+        <v>442.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-29T21:28:26</t>
+          <t>2026-10-29T21:29:04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5776.8</v>
+        <v>5714.3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-29T21:28:26</t>
+          <t>2026-10-29T21:29:04</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>442.5</v>
+        <v>453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-29T21:29:04</t>
+          <t>2026-10-29T21:29:50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-29T21:29:04</t>
+          <t>2026-10-29T21:29:50</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>453</v>
+        <v>447.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-29T21:29:50</t>
+          <t>2026-10-29T21:30:34</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5714.3</v>
+        <v>5614.3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-29T21:29:50</t>
+          <t>2026-10-29T21:30:34</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>447.5</v>
+        <v>446.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-29T21:30:34</t>
+          <t>2026-10-29T21:31:10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5614.3</v>
+        <v>5564.3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-29T21:30:34</t>
+          <t>2026-10-29T21:31:10</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-29T21:31:10</t>
+          <t>2026-10-29T21:31:48</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5564.3</v>
+        <v>5551.8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-29T21:31:10</t>
+          <t>2026-10-29T21:31:48</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-29T21:31:48</t>
+          <t>2026-10-29T21:32:21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5551.8</v>
+        <v>5551.75</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-29T21:31:48</t>
+          <t>2026-10-29T21:32:21</t>
         </is>
       </c>
     </row>

--- a/data/latest_prices.xlsx
+++ b/data/latest_prices.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>446.5</v>
+        <v>449.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -488,13 +488,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-29T21:32:21</t>
+          <t>2026-10-30T22:34:07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5551.75</v>
+        <v>5344.25</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-29T21:32:21</t>
+          <t>2026-10-30T22:34:07</t>
         </is>
       </c>
     </row>
